--- a/data/trans_orig/P33_MIN_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Provincia-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Nº medio de minutos durante los cuales la población se echa la siesta</t>
+          <t>Nº medio de minutos durante los cuales la población se echa la siesta (tasa de respuesta: 37,35%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 44,74</t>
+          <t>28,35; 43,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,55; 59,17</t>
+          <t>43,28; 58,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,27; 48,18</t>
+          <t>36,79; 48,11</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 50,36</t>
+          <t>32,85; 49,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 45,14</t>
+          <t>30,06; 44,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,52; 44,64</t>
+          <t>33,63; 44,48</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 32,84</t>
+          <t>19,3; 32,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,54; 42,68</t>
+          <t>17,24; 42,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,34; 32,19</t>
+          <t>20,02; 32,6</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,22; 42,04</t>
+          <t>30,17; 42,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 49,64</t>
+          <t>24,61; 47,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,58; 41,69</t>
+          <t>28,7; 42,01</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 61,7</t>
+          <t>44,6; 61,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,91; 51,6</t>
+          <t>35,89; 51,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,77; 54,45</t>
+          <t>42,13; 53,92</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,98; 41,3</t>
+          <t>20,09; 41,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 29,42</t>
+          <t>11,02; 27,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,75; 33,39</t>
+          <t>18,45; 33,18</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,09; 33,54</t>
+          <t>23,35; 33,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,87; 33,18</t>
+          <t>4,33; 33,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,48; 30,82</t>
+          <t>8,11; 31,14</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,99; 55,29</t>
+          <t>11,45; 55,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,82; 50,16</t>
+          <t>44,74; 50,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14,75; 51,32</t>
+          <t>16,75; 51,65</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,8; 39,11</t>
+          <t>18,75; 39,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,02; 38,22</t>
+          <t>17,58; 38,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,82; 37,62</t>
+          <t>23,07; 38,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_MIN_2023_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33_MIN_2023_R-Provincia-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36,29</t>
+          <t>38,52</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50,53</t>
+          <t>51,97</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42,37</t>
+          <t>44,43</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,35; 43,23</t>
+          <t>31,53; 45,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,28; 58,96</t>
+          <t>45,32; 60,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,79; 48,11</t>
+          <t>39,34; 49,96</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40,51</t>
+          <t>38,59</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36,39</t>
+          <t>37,05</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,62</t>
+          <t>37,87</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 49,27</t>
+          <t>31,33; 46,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 44,54</t>
+          <t>30,8; 44,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,48</t>
+          <t>33,35; 43,98</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25,49</t>
+          <t>26,93</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24,72</t>
+          <t>24,94</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25,16</t>
+          <t>26,07</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,3; 32,96</t>
+          <t>20,52; 35,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,24; 42,15</t>
+          <t>17,43; 44,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,02; 32,6</t>
+          <t>21,0; 34,23</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>35,05</t>
+          <t>33,61</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30,95</t>
+          <t>31,78</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33,2</t>
+          <t>32,81</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,17; 42,1</t>
+          <t>28,3; 41,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,61; 47,1</t>
+          <t>25,07; 48,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,7; 42,01</t>
+          <t>28,26; 40,11</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52,85</t>
+          <t>53,07</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,76</t>
+          <t>43,24</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>48,09</t>
+          <t>48,07</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,6; 61,7</t>
+          <t>44,64; 62,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,89; 51,12</t>
+          <t>35,61; 50,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,13; 53,92</t>
+          <t>41,99; 54,01</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28,4</t>
+          <t>28,23</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,38</t>
+          <t>17,17</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24,34</t>
+          <t>24,12</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,09; 41,39</t>
+          <t>20,9; 40,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 27,85</t>
+          <t>11,07; 29,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,45; 33,18</t>
+          <t>18,88; 32,27</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>28,27</t>
+          <t>29,38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,56</t>
+          <t>30,33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,14</t>
+          <t>29,83</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23,35; 33,9</t>
+          <t>24,6; 34,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 33,16</t>
+          <t>24,55; 37,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,11; 31,14</t>
+          <t>26,29; 34,56</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30,02</t>
+          <t>53,53</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47,52</t>
+          <t>47,33</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36,28</t>
+          <t>50,43</t>
         </is>
       </c>
     </row>
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,45; 55,37</t>
+          <t>49,95; 58,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,74; 50,08</t>
+          <t>44,69; 50,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,75; 51,65</t>
+          <t>48,02; 53,54</t>
         </is>
       </c>
     </row>
@@ -948,17 +948,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>32,14</t>
+          <t>38,44</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31,47</t>
+          <t>37,51</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31,83</t>
+          <t>38,01</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,75; 39,01</t>
+          <t>36,09; 41,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17,58; 38,11</t>
+          <t>35,23; 40,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,07; 38,27</t>
+          <t>36,36; 39,82</t>
         </is>
       </c>
     </row>
